--- a/artfynd/A 50342-2025 artfynd.xlsx
+++ b/artfynd/A 50342-2025 artfynd.xlsx
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>

--- a/artfynd/A 50342-2025 artfynd.xlsx
+++ b/artfynd/A 50342-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112241786</v>
+        <v>112241725</v>
       </c>
       <c r="B2" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553747</v>
+        <v>553520</v>
       </c>
       <c r="R2" t="n">
-        <v>7031459</v>
+        <v>7031193</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112241775</v>
+        <v>112241726</v>
       </c>
       <c r="B3" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554004</v>
+        <v>553638</v>
       </c>
       <c r="R3" t="n">
-        <v>7031306</v>
+        <v>7031010</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,43 +869,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112241765</v>
+        <v>112241805</v>
       </c>
       <c r="B4" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554072</v>
+        <v>553710</v>
       </c>
       <c r="R4" t="n">
-        <v>7031075</v>
+        <v>7030934</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +947,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,6 +956,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,43 +975,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112241762</v>
+        <v>112241806</v>
       </c>
       <c r="B5" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554067</v>
+        <v>553629</v>
       </c>
       <c r="R5" t="n">
-        <v>7031041</v>
+        <v>7031222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1053,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,6 +1062,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1119,32 +1081,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112241763</v>
+        <v>112241792</v>
       </c>
       <c r="B6" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1153,20 +1110,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554060</v>
+        <v>553692</v>
       </c>
       <c r="R6" t="n">
-        <v>7031065</v>
+        <v>7031552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,11 +1152,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,15 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112241756</v>
+        <v>112241749</v>
       </c>
       <c r="B7" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553932</v>
+        <v>553689</v>
       </c>
       <c r="R7" t="n">
-        <v>7031216</v>
+        <v>7031093</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,15 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112241773</v>
+        <v>112241751</v>
       </c>
       <c r="B8" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554032</v>
+        <v>553688</v>
       </c>
       <c r="R8" t="n">
-        <v>7031267</v>
+        <v>7031096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,15 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112241770</v>
+        <v>112241752</v>
       </c>
       <c r="B9" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554059</v>
+        <v>553678</v>
       </c>
       <c r="R9" t="n">
-        <v>7031183</v>
+        <v>7031113</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,15 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112241758</v>
+        <v>112241753</v>
       </c>
       <c r="B10" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553989</v>
+        <v>553877</v>
       </c>
       <c r="R10" t="n">
-        <v>7031142</v>
+        <v>7031321</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,50 +1602,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112241726</v>
+        <v>112241754</v>
       </c>
       <c r="B11" t="n">
-        <v>90276</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553638</v>
+        <v>553896</v>
       </c>
       <c r="R11" t="n">
-        <v>7031011</v>
+        <v>7031323</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,6 +1677,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,15 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112241784</v>
+        <v>112241755</v>
       </c>
       <c r="B12" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553885</v>
+        <v>553921</v>
       </c>
       <c r="R12" t="n">
-        <v>7031458</v>
+        <v>7031223</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,15 +1814,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112241755</v>
+        <v>112241756</v>
       </c>
       <c r="B13" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553921</v>
+        <v>553932</v>
       </c>
       <c r="R13" t="n">
-        <v>7031223</v>
+        <v>7031216</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,15 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112241760</v>
+        <v>112241757</v>
       </c>
       <c r="B14" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553969</v>
+        <v>553976</v>
       </c>
       <c r="R14" t="n">
-        <v>7031101</v>
+        <v>7031190</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,15 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112241803</v>
+        <v>112241758</v>
       </c>
       <c r="B15" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,34 +2037,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553821</v>
+        <v>553989</v>
       </c>
       <c r="R15" t="n">
-        <v>7031543</v>
+        <v>7031142</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,6 +2101,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,15 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112241802</v>
+        <v>112241760</v>
       </c>
       <c r="B16" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,34 +2143,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553769</v>
+        <v>553969</v>
       </c>
       <c r="R16" t="n">
-        <v>7031463</v>
+        <v>7031102</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,6 +2207,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,15 +2238,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112241789</v>
+        <v>112241761</v>
       </c>
       <c r="B17" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553799</v>
+        <v>554045</v>
       </c>
       <c r="R17" t="n">
-        <v>7031561</v>
+        <v>7031028</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,15 +2344,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112241799</v>
+        <v>112241762</v>
       </c>
       <c r="B18" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,34 +2355,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553977</v>
+        <v>554067</v>
       </c>
       <c r="R18" t="n">
-        <v>7031205</v>
+        <v>7031041</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2500,6 +2419,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2526,15 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112241764</v>
+        <v>112241763</v>
       </c>
       <c r="B19" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>554059</v>
+        <v>554060</v>
       </c>
       <c r="R19" t="n">
-        <v>7031070</v>
+        <v>7031065</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,15 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112241782</v>
+        <v>112241764</v>
       </c>
       <c r="B20" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,10 +2595,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553879</v>
+        <v>554059</v>
       </c>
       <c r="R20" t="n">
-        <v>7031424</v>
+        <v>7031070</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,15 +2662,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112241788</v>
+        <v>112241765</v>
       </c>
       <c r="B21" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,11 +2693,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2796,10 +2701,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553821</v>
+        <v>554072</v>
       </c>
       <c r="R21" t="n">
-        <v>7031543</v>
+        <v>7031075</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,11 +2739,16 @@
           <t>2023-09-20</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
@@ -2858,15 +2768,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112241800</v>
+        <v>112241766</v>
       </c>
       <c r="B22" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,34 +2779,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>554037</v>
+        <v>554072</v>
       </c>
       <c r="R22" t="n">
-        <v>7031059</v>
+        <v>7031070</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,6 +2843,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2960,15 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112241749</v>
+        <v>112241767</v>
       </c>
       <c r="B23" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>553689</v>
+        <v>554066</v>
       </c>
       <c r="R23" t="n">
-        <v>7031093</v>
+        <v>7031096</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3071,15 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112241806</v>
+        <v>112241768</v>
       </c>
       <c r="B24" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,26 +2991,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3114,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553629</v>
+        <v>554088</v>
       </c>
       <c r="R24" t="n">
-        <v>7031222</v>
+        <v>7031118</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,7 +3059,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3163,7 +3068,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3182,15 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112241785</v>
+        <v>112241769</v>
       </c>
       <c r="B25" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3226,10 +3125,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>553783</v>
+        <v>554083</v>
       </c>
       <c r="R25" t="n">
-        <v>7031447</v>
+        <v>7031130</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3293,15 +3192,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112241787</v>
+        <v>112241770</v>
       </c>
       <c r="B26" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,10 +3231,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553807</v>
+        <v>554059</v>
       </c>
       <c r="R26" t="n">
-        <v>7031536</v>
+        <v>7031183</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3404,15 +3298,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112241805</v>
+        <v>112241771</v>
       </c>
       <c r="B27" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3420,26 +3309,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3447,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>553710</v>
+        <v>554042</v>
       </c>
       <c r="R27" t="n">
-        <v>7030934</v>
+        <v>7031192</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,7 +3377,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3496,7 +3386,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3515,15 +3404,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112241766</v>
+        <v>112241772</v>
       </c>
       <c r="B28" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,10 +3443,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>554072</v>
+        <v>554055</v>
       </c>
       <c r="R28" t="n">
-        <v>7031070</v>
+        <v>7031223</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3626,15 +3510,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112241772</v>
+        <v>112241773</v>
       </c>
       <c r="B29" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3670,10 +3549,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>554055</v>
+        <v>554033</v>
       </c>
       <c r="R29" t="n">
-        <v>7031223</v>
+        <v>7031268</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3737,15 +3616,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112241754</v>
+        <v>112241774</v>
       </c>
       <c r="B30" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,10 +3655,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>553896</v>
+        <v>554013</v>
       </c>
       <c r="R30" t="n">
-        <v>7031322</v>
+        <v>7031308</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3848,15 +3722,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112241752</v>
+        <v>112241775</v>
       </c>
       <c r="B31" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,10 +3761,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>553678</v>
+        <v>554004</v>
       </c>
       <c r="R31" t="n">
-        <v>7031113</v>
+        <v>7031306</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3959,15 +3828,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112241801</v>
+        <v>112241776</v>
       </c>
       <c r="B32" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3975,34 +3839,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>553907</v>
+        <v>553962</v>
       </c>
       <c r="R32" t="n">
-        <v>7031359</v>
+        <v>7031302</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4035,6 +3903,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4061,15 +3934,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112241783</v>
+        <v>112241777</v>
       </c>
       <c r="B33" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4105,10 +3973,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>553891</v>
+        <v>553949</v>
       </c>
       <c r="R33" t="n">
-        <v>7031451</v>
+        <v>7031315</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4172,15 +4040,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112241774</v>
+        <v>112241778</v>
       </c>
       <c r="B34" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4216,10 +4079,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>554013</v>
+        <v>553946</v>
       </c>
       <c r="R34" t="n">
-        <v>7031308</v>
+        <v>7031358</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4283,15 +4146,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112241771</v>
+        <v>112241779</v>
       </c>
       <c r="B35" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4327,10 +4185,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>554043</v>
+        <v>553896</v>
       </c>
       <c r="R35" t="n">
-        <v>7031191</v>
+        <v>7031368</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4394,15 +4252,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112241778</v>
+        <v>112241780</v>
       </c>
       <c r="B36" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4438,10 +4291,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>553947</v>
+        <v>553888</v>
       </c>
       <c r="R36" t="n">
-        <v>7031358</v>
+        <v>7031403</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4505,15 +4358,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112241780</v>
+        <v>112241781</v>
       </c>
       <c r="B37" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4538,21 +4386,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>553888</v>
+        <v>553886</v>
       </c>
       <c r="R37" t="n">
-        <v>7031403</v>
+        <v>7031410</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4585,11 +4445,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4616,15 +4471,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112241777</v>
+        <v>112241782</v>
       </c>
       <c r="B38" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4660,10 +4510,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553949</v>
+        <v>553879</v>
       </c>
       <c r="R38" t="n">
-        <v>7031315</v>
+        <v>7031425</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4727,15 +4577,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112241751</v>
+        <v>112241783</v>
       </c>
       <c r="B39" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4771,10 +4616,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553688</v>
+        <v>553891</v>
       </c>
       <c r="R39" t="n">
-        <v>7031096</v>
+        <v>7031452</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4838,15 +4683,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112241767</v>
+        <v>112241784</v>
       </c>
       <c r="B40" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4882,10 +4722,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>554066</v>
+        <v>553885</v>
       </c>
       <c r="R40" t="n">
-        <v>7031096</v>
+        <v>7031457</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4949,15 +4789,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112241791</v>
+        <v>112241785</v>
       </c>
       <c r="B41" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4983,16 +4818,20 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>553764</v>
+        <v>553782</v>
       </c>
       <c r="R41" t="n">
-        <v>7031567</v>
+        <v>7031447</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5025,6 +4864,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5051,15 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112241757</v>
+        <v>112241786</v>
       </c>
       <c r="B42" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5095,10 +4934,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>553975</v>
+        <v>553747</v>
       </c>
       <c r="R42" t="n">
-        <v>7031190</v>
+        <v>7031459</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5162,15 +5001,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112241753</v>
+        <v>112241787</v>
       </c>
       <c r="B43" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5206,10 +5040,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>553877</v>
+        <v>553807</v>
       </c>
       <c r="R43" t="n">
-        <v>7031320</v>
+        <v>7031535</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5273,15 +5107,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112241776</v>
+        <v>112241788</v>
       </c>
       <c r="B44" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5309,7 +5138,11 @@
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5317,10 +5150,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>553962</v>
+        <v>553821</v>
       </c>
       <c r="R44" t="n">
-        <v>7031303</v>
+        <v>7031542</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5355,16 +5188,11 @@
           <t>2023-09-20</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5384,15 +5212,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112241781</v>
+        <v>112241789</v>
       </c>
       <c r="B45" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5417,33 +5240,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>553886</v>
+        <v>553799</v>
       </c>
       <c r="R45" t="n">
-        <v>7031411</v>
+        <v>7031561</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5476,6 +5287,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5502,15 +5318,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112241804</v>
+        <v>112241790</v>
       </c>
       <c r="B46" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5518,34 +5329,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>553769</v>
+        <v>553773</v>
       </c>
       <c r="R46" t="n">
-        <v>7031533</v>
+        <v>7031575</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5578,6 +5393,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5604,15 +5424,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112241779</v>
+        <v>112241791</v>
       </c>
       <c r="B47" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5638,20 +5453,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>stormyrberget Björkvattnet, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>553897</v>
+        <v>553764</v>
       </c>
       <c r="R47" t="n">
-        <v>7031369</v>
+        <v>7031567</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5684,11 +5495,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5715,53 +5521,55 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112241725</v>
+        <v>69739851</v>
       </c>
       <c r="B48" t="n">
-        <v>90276</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>stormyrberget Björkvattnet, Ång</t>
+          <t>Stormyrberget/ Björkvattent, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>553520</v>
+        <v>553567</v>
       </c>
       <c r="R48" t="n">
-        <v>7031193</v>
+        <v>7031017</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5785,12 +5593,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2017-09-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2017-09-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5805,15 +5613,128 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Askia Sandberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Askia Sandberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>112241795</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>stormyrberget Björkvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>553669</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7031201</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50342-2025 artfynd.xlsx
+++ b/artfynd/A 50342-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241725</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241726</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241805</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241806</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241792</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241749</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241751</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241752</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241753</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1705,6 +1755,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241754</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241755</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1917,6 +1977,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241756</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241757</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2129,6 +2199,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241758</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2235,6 +2310,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241760</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2341,6 +2421,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241761</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2447,6 +2532,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241762</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2553,6 +2643,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241763</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2659,6 +2754,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241764</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2765,6 +2865,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241765</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2871,6 +2976,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241766</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2977,6 +3087,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241767</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3083,6 +3198,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241768</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3189,6 +3309,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241769</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3295,6 +3420,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241770</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3401,6 +3531,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241771</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3507,6 +3642,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241772</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3613,6 +3753,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241773</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3719,6 +3864,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241774</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3825,6 +3975,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241775</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3931,6 +4086,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241776</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4037,6 +4197,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241777</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4143,6 +4308,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241778</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4249,6 +4419,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241779</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4355,6 +4530,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241780</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4468,6 +4648,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241781</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4574,6 +4759,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241782</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4680,6 +4870,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241783</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4786,6 +4981,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241784</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4892,6 +5092,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241785</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4998,6 +5203,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241786</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5104,6 +5314,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241787</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5209,6 +5424,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241788</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5315,6 +5535,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241789</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5421,6 +5646,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241790</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5518,6 +5748,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241791</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5626,6 +5861,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69739851</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5735,8 +5975,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112241795</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>